--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.6" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00138_18940629.6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.6.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -991,7 +991,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.6.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00138_18940629.6" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.6" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ly healthy. (Oh, oh) ã€� shall be pleased</t>
+          <t>L144: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E | isolated marker/symbol line :: 美</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 1 â€¢ tor. Conveyancer, etc. Office-23 James</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29, 1894.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29, 1894.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L35: isolated marker/symbol line :: O</t>
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,19 +704,19 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L254: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L254: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. B.â€”Money to loan on real estate.</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 1 • tor. Conveyancer, etc. Office-23 James</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L163: symbol-only separator/garbage line :: $100, 000</t>
+          <t>L144: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E | isolated marker/symbol line :: 美</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -783,19 +787,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L426: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L402: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: terms of repayment. Officeâ€”No. 8 Main</t>
+          <t>L382: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: 7</t>
+          <t>L163: symbol-only separator/garbage line :: $100, 000</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -838,12 +842,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>136</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -866,24 +870,24 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L436: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L403: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, June 28.â€”In the House of</t>
+          <t>L623: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Accom.................•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L203: symbol-only separator/garbage line :: 9.05</t>
+          <t>L188: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L382: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -945,19 +949,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L444: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L416: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. Leightonâ€”" Is not excessive tea</t>
+          <t>L905: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: '• Thank you," he responded, accepting</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L204: symbol-only separator/garbage line :: 9.15</t>
+          <t>L203: symbol-only separator/garbage line :: 9.05</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -982,7 +986,7 @@
       <c r="V6" s="1" t="inlineStr"/>
       <c r="W6" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: 2 to 5 p.m. Dr. Batesâ€™ residence. No. 53 Augusta</t>
+          <t>L763: abbreviation/spacing may be garbled :: 2 to 5 p.m. Dr. Bates’ residence. No. 53 Augusta</t>
         </is>
       </c>
       <c r="X6" s="1" t="inlineStr"/>
@@ -1020,19 +1024,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L424: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mr. Morleyâ€”" I must confine myself en-</t>
+          <t>L1171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • materials, we will offer Dress Goods•</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L226: symbol-only separator/garbage line :: 5.35</t>
+          <t>L204: symbol-only separator/garbage line :: 9.15</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1095,19 +1099,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L434: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pareilâ€”12 lines to the inch.</t>
+          <t>L1172: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+25BA BLACK RIGHT-POINTING POINTER :: •►at the cost price and in some instances 1,</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L227: symbol-only separator/garbage line :: 5.40</t>
+          <t>L226: symbol-only separator/garbage line :: 5.35</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1170,19 +1174,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L487: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L446: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: How to Save the Spark of Lifeâ€”A Set of</t>
+          <t>L1173: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: $at even less than what we paid for•</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L237: symbol-only separator/garbage line :: 6.38</t>
+          <t>L227: symbol-only separator/garbage line :: 5.40</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1199,7 +1203,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L1182: line starts with punctuation glued to text | suspicious token(s): Dress2 (letter/digit mix) :: *All light shades in Woolen Dress2</t>
+          <t>L1171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • materials, we will offer Dress Goods•</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1221,12 +1225,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1245,19 +1249,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L485: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L294: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: beryâ€™s remarks by stating that the pres-</t>
+          <t>L1174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •them.•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L238: symbol-only separator/garbage line :: 6.47</t>
+          <t>L237: symbol-only separator/garbage line :: 6.38</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1272,7 +1276,11 @@
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>L1174: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •them.•</t>
+        </is>
+      </c>
       <c r="T10" s="1" t="inlineStr"/>
       <c r="U10" s="1" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr"/>
@@ -1297,7 +1305,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1311,24 +1319,24 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 9a (letter/digit mix) :: street, Toronto. Office hour â€”9a. m. tolp.Â».,</t>
+          <t>L762: suspicious token(s): 9a (letter/digit mix) :: street, Toronto. Office hour —9a. m. tolp.».,</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L504: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Billâ€”Immigrant Drowned-Attempt to</t>
+          <t>L1175: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: •The balance of the 25c, 28c and 30c$</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L246: symbol-only separator/garbage line :: 8.00</t>
+          <t>L238: symbol-only separator/garbage line :: 6.47</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1343,13 +1351,17 @@
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>L1175: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: •The balance of the 25c, 28c and 30c$</t>
+        </is>
+      </c>
       <c r="T11" s="1" t="inlineStr"/>
       <c r="U11" s="1" t="inlineStr"/>
       <c r="V11" s="1" t="inlineStr"/>
       <c r="W11" s="1" t="inlineStr">
         <is>
-          <t>L1074: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: From Dundas.â€”6.10, 8.00. 9.00, 10 15, 11.15 a.m.,</t>
+          <t>L1074: abbreviation/spacing may be garbled :: From Dundas.—6.10, 8.00. 9.00, 10 15, 11.15 a.m.,</t>
         </is>
       </c>
       <c r="X11" s="1" t="inlineStr"/>
@@ -1363,12 +1375,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1387,19 +1399,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L844: stray/suspicious non-ASCII glyph(s): U+96EA CJK UNIFIED IDEOGRAPH-96EA | isolated marker/symbol line :: 雪</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Casimir-Perierâ€™s</t>
+          <t>L1177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-wool•</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L247: symbol-only separator/garbage line :: 8.20</t>
+          <t>L246: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1414,7 +1426,11 @@
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
-      <c r="S12" s="1" t="inlineStr"/>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>L1178: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Delaines at 19%ca yard.$</t>
+        </is>
+      </c>
       <c r="T12" s="1" t="inlineStr"/>
       <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr"/>
@@ -1454,19 +1470,19 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L908: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Barnardoâ€™s home started from Lottion</t>
+          <t>L1178: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Delaines at 19%ca yard.$</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L253: isolated marker/symbol line :: 50</t>
+          <t>L247: symbol-only separator/garbage line :: 8.20</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1481,7 +1497,11 @@
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>L1181: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All Spotted White Muslins at cost.X</t>
+        </is>
+      </c>
       <c r="T13" s="1" t="inlineStr"/>
       <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr"/>
@@ -1502,7 +1522,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1519,21 +1539,17 @@
           <t>L1098: suspicious token(s): 50c (letter/digit mix) :: need a set of teeth? Best $8; gas 50c. Pleasant;</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L524: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L355: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: M. Casimir-Perierâ€™s election is an augury</t>
+          <t>L1180: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L254: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L253: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1548,7 +1564,11 @@
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>L1182: line starts with punctuation glued to text | suspicious token(s): Dress2 (letter/digit mix) :: *All light shades in Woolen Dress2</t>
+        </is>
+      </c>
       <c r="T14" s="1" t="inlineStr"/>
       <c r="U14" s="1" t="inlineStr"/>
       <c r="V14" s="1" t="inlineStr"/>
@@ -1586,21 +1606,17 @@
           <t>L1103: suspicious token(s): McLAUGHLIN (odd internal casing) :: IR. McLAUGHLIN, DENTIST,</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L530: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Yesterdayâ€™s session of the United States</t>
+          <t>L1181: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All Spotted White Muslins at cost.X</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L283: symbol-only separator/garbage line :: 7.10</t>
+          <t>L254: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1615,7 +1631,11 @@
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L1184: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •The choice of the balance of our•</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1650,24 +1670,20 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>L1175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: â€¢The balance of the 25c, 28c and 30c$</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: as follows:â€œAs the House has not</t>
-        </is>
-      </c>
+          <t>L1175: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: •The balance of the 25c, 28c and 30c$</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1183: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: $Materials at cost and under.•</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L294: symbol-only separator/garbage line :: 8.35</t>
+          <t>L283: symbol-only separator/garbage line :: 7.10</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1682,7 +1698,11 @@
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>L1187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 40c (letter/digit mix) :: • 40c a yard. .•</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr"/>
@@ -1720,21 +1740,17 @@
           <t>L1176: punctuation artifact: repeated periods | suspicious token(s): 20c (letter/digit mix) :: : : French Crinkle at 20c a yard..-</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L837: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L432: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: may say â€˜Rot,â€™" continued Mr. Keir</t>
+          <t>L1184: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •The choice of the balance of our•</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L295: symbol-only separator/garbage line :: 8.40</t>
+          <t>L294: symbol-only separator/garbage line :: 8.35</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1745,11 +1761,15 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Accom.................â€¢</t>
+          <t>L623: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Accom.................•</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 59c (letter/digit mix) :: • colors, at 59c each. •</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" s="1" t="inlineStr"/>
@@ -1772,24 +1792,20 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>L1177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-woolâ€¢</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L908: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
-        </is>
-      </c>
+          <t>L1177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-wool•</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GEORGE LYNCH-STAUNTON, Arthur Oâ€™HEIR.</t>
+          <t>L1185: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 1• latest and very stylish Dress Materials,$</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L303: symbol-only separator/garbage line :: 9.05</t>
+          <t>L295: symbol-only separator/garbage line :: 8.40</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1804,7 +1820,11 @@
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>L1196: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 75c (letter/digit mix) :: • Ladies’ Umbrellas at 75c each. *</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" s="1" t="inlineStr"/>
@@ -1833,14 +1853,14 @@
       <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: TRAVELLERSâ€™</t>
+          <t>L1186: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, for•</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L304: symbol-only separator/garbage line :: 9.05</t>
+          <t>L303: symbol-only separator/garbage line :: 9.05</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1855,7 +1875,11 @@
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>L1200: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 5c (letter/digit mix) :: • Ladies’ Vests at 5c each °</t>
+        </is>
+      </c>
       <c r="T19" s="1" t="inlineStr"/>
       <c r="U19" s="1" t="inlineStr"/>
       <c r="V19" s="1" t="inlineStr"/>
@@ -1878,20 +1902,20 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>L1180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.â€¢</t>
+          <t>L1180: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.•</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L565: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 36 James street south, over Molsonâ€™s Bank.</t>
+          <t>L1187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 40c (letter/digit mix) :: • 40c a yard. .•</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L312: isolated marker/symbol line :: D</t>
+          <t>L304: symbol-only separator/garbage line :: 9.05</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1906,7 +1930,11 @@
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>L1204: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All kinds of Silk Lace Mitts, in•</t>
+        </is>
+      </c>
       <c r="T20" s="1" t="inlineStr"/>
       <c r="U20" s="1" t="inlineStr"/>
       <c r="V20" s="1" t="inlineStr"/>
@@ -1935,14 +1963,14 @@
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: small amounts. No commission or agentâ€™s fees.</t>
+          <t>L1189: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 1•The balance of a line we sold at $12</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L319: symbol-only separator/garbage line :: 9.53</t>
+          <t>L312: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1957,7 +1985,11 @@
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • at cost.</t>
+        </is>
+      </c>
       <c r="T21" s="1" t="inlineStr"/>
       <c r="U21" s="1" t="inlineStr"/>
       <c r="V21" s="1" t="inlineStr"/>
@@ -1980,20 +2012,20 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>L1186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, forâ€¢</t>
+          <t>L1186: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, for•</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Accom.................â€¢</t>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 59c (letter/digit mix) :: • colors, at 59c each. •</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L320: symbol-only separator/garbage line :: 10.00</t>
+          <t>L319: symbol-only separator/garbage line :: 9.53</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2031,20 +2063,20 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>L1187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 40c (letter/digit mix) :: â€¢ 40c a yard. .â€¢</t>
+          <t>L1187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 40c (letter/digit mix) :: • 40c a yard. .•</t>
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: city property. No agentâ€™s fees or commission</t>
+          <t>L1196: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 75c (letter/digit mix) :: • Ladies’ Umbrellas at 75c each. *</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L326: symbol-only separator/garbage line :: 8.25</t>
+          <t>L320: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2082,20 +2114,20 @@
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>L1190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1â€˜a yard reduced for this sale to 50c a --</t>
+          <t>L1190: punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1‘a yard reduced for this sale to 50c a --</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 9a (letter/digit mix) :: street, Toronto. Office hour â€”9a. m. tolp.Â».,</t>
+          <t>L1198: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: • $1.50 each. •</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L327: symbol-only separator/garbage line :: 9.20</t>
+          <t>L326: symbol-only separator/garbage line :: 8.25</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2133,20 +2165,20 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>L1194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 59c (letter/digit mix) :: â€¢ colors, at 59c each. â€¢</t>
+          <t>L1194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 59c (letter/digit mix) :: • colors, at 59c each. •</t>
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: 2 to 5 p.m. Dr. Batesâ€™ residence. No. 53 Augusta</t>
+          <t>L1200: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 5c (letter/digit mix) :: • Ladies’ Vests at 5c each °</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L336: symbol-only separator/garbage line :: 11.05</t>
+          <t>L327: symbol-only separator/garbage line :: 9.20</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2184,20 +2216,20 @@
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>L1196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 75c (letter/digit mix) :: â€¢ Ladiesâ€™ Umbrellas at 75c each. *</t>
+          <t>L1196: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 75c (letter/digit mix) :: • Ladies’ Umbrellas at 75c each. *</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Toronto Express........9.10â€”</t>
+          <t>L1203: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: %each.•</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L346: isolated marker/symbol line :: a</t>
+          <t>L336: symbol-only separator/garbage line :: 11.05</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2235,20 +2267,20 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>L1200: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 5c (letter/digit mix) :: â€¢ Ladiesâ€™ Vests at 5c each Â°</t>
+          <t>L1200: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text | suspicious token(s): 5c (letter/digit mix) :: • Ladies’ Vests at 5c each °</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nitrous oxide adminisâ€™ ered.</t>
+          <t>L1204: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • All kinds of Silk Lace Mitts, in•</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L358: symbol-only separator/garbage line :: 6.40</t>
+          <t>L346: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2259,7 +2291,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Toronto Express........9.10â€”</t>
+          <t>L802: punctuation artifact: repeated periods :: Toronto Express........9.10—</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2292,14 +2324,14 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>L905: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 'â€¢ Thank you," he responded, accepting</t>
+          <t>L1205: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: : • black, cream and fawn, at cost. 1:</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L359: symbol-only separator/garbage line :: 6.55</t>
+          <t>L358: symbol-only separator/garbage line :: 6.40</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2343,14 +2375,14 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: For Gentsâ€™ Summer Underwear, Socks,</t>
+          <t>L1207: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: %The balance of new Lace Curtains•</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L364: symbol-only separator/garbage line :: 9.10</t>
+          <t>L359: symbol-only separator/garbage line :: 6.55</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2390,14 +2422,14 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>L1010: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: flector.â€”House Furnishing Review.</t>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • at cost.</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L371: isolated marker/symbol line :: A</t>
+          <t>L364: symbol-only separator/garbage line :: 9.10</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2437,14 +2469,14 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>L1025: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Runs on Sundays, but does not stop at inter-</t>
+          <t>L1226: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: = •</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L401: symbol-only separator/garbage line :: 9.20</t>
+          <t>L371: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2455,7 +2487,7 @@
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L1190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1â€˜a yard reduced for this sale to 50c a --</t>
+          <t>L1190: punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1‘a yard reduced for this sale to 50c a --</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2484,14 +2516,14 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>L1074: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: From Dundas.â€”6.10, 8.00. 9.00, 10 15, 11.15 a.m.,</t>
+          <t>L1444: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ed from life from people cured, free by mail.■</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L405: symbol-only separator/garbage line :: 10.25</t>
+          <t>L401: symbol-only separator/garbage line :: 9.20</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
@@ -2529,16 +2561,12 @@
       </c>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: corner Mary. â€˜Phone 1,192.</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L413: symbol-only separator/garbage line :: 11.10</t>
+          <t>L402: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2572,16 +2600,12 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L1114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cayuga, Ont., June 28.â€”There was a</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L415: symbol-only separator/garbage line :: 1.50</t>
+          <t>L403: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2615,16 +2639,12 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L1123: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: was fractured. â€˜Wm. Stevenson,jr.,</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L423: symbol-only separator/garbage line :: 4.10</t>
+          <t>L405: symbol-only separator/garbage line :: 10.25</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2654,16 +2674,12 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L1137: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Fletcherâ€™s planing mills, Yonge street,</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L425: symbol-only separator/garbage line :: 5.25</t>
+          <t>L413: symbol-only separator/garbage line :: 11.10</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2693,16 +2709,12 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L1148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: where the injured arm â€žas amputated.</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L433: symbol-only separator/garbage line :: 5.40</t>
+          <t>L415: symbol-only separator/garbage line :: 1.50</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2732,16 +2744,12 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L1171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ materials, we will offer Dress Goodsâ€¢</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L435: symbol-only separator/garbage line :: 7.05</t>
+          <t>L416: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2771,16 +2779,12 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L1172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â–ºat the cost price and in some instances 1,</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L443: symbol-only separator/garbage line :: 6.55</t>
+          <t>L423: symbol-only separator/garbage line :: 4.10</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -2810,16 +2814,12 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L1173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: $at even less than what we paid forâ€¢</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L445: symbol-only separator/garbage line :: 8.10</t>
+          <t>L424: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
@@ -2849,16 +2849,12 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L1174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢them.â€¢</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L450: isolated marker/symbol line :: a</t>
+          <t>L425: symbol-only separator/garbage line :: 5.25</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
@@ -2888,21 +2884,17 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L1175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix), 28c (letter/digit mix), 30c (letter/digit mix) :: â€¢The balance of the 25c, 28c and 30c$</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L451: symbol-only separator/garbage line :: 9.20</t>
+          <t>L426: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L1300: isolated marker/symbol line :: "</t>
+          <t>L1226: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: = •</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2927,21 +2919,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L1177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 30c (letter/digit mix) :: $All that's left of the 30c All-woolâ€¢</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L453: symbol-only separator/garbage line :: 10.30</t>
+          <t>L433: symbol-only separator/garbage line :: 5.40</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L1364: symbol-only separator/garbage line :: *****************-</t>
+          <t>L1300: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2966,21 +2954,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L1178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Delaines at 19%ca yard.$</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L464: isolated marker/symbol line :: D.</t>
+          <t>L434: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L1368: symbol-only separator/garbage line :: ***************</t>
+          <t>L1364: symbol-only separator/garbage line :: *****************-</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3005,21 +2989,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 25c (letter/digit mix) :: %25c a yard.â€¢</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L484: symbol-only separator/garbage line :: 8.45</t>
+          <t>L435: symbol-only separator/garbage line :: 7.05</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L1374: isolated marker/symbol line :: 0</t>
+          <t>L1368: symbol-only separator/garbage line :: ***************</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3044,21 +3024,17 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ All Spotted White Muslins at cost.X</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L486: symbol-only separator/garbage line :: 9.65</t>
+          <t>L436: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L1439: isolated marker/symbol line :: *</t>
+          <t>L1374: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3083,21 +3059,17 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1183: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: $Materials at cost and under.â€¢</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L487: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L443: symbol-only separator/garbage line :: 6.55</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L1450: isolated marker/symbol line :: :</t>
+          <t>L1439: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -3122,21 +3094,17 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1184: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢The choice of the balance of ourâ€¢</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L489: isolated marker/symbol line :: R.</t>
+          <t>L444: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L1467: symbol-only separator/garbage line :: *********************</t>
+          <t>L1450: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -3161,21 +3129,17 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 1â€¢ latest and very stylish Dress Materials,$</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L501: symbol-only separator/garbage line :: 2.50</t>
+          <t>L445: symbol-only separator/garbage line :: 8.10</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L1477: isolated marker/symbol line :: -</t>
+          <t>L1467: symbol-only separator/garbage line :: *********************</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3200,19 +3164,19 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 60c (letter/digit mix) :: $selling heretotore at 60c a yard, forâ€¢</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L503: symbol-only separator/garbage line :: 3.55</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr"/>
+          <t>L446: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L1477: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3235,16 +3199,12 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 40c (letter/digit mix) :: â€¢ 40c a yard. .â€¢</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: 455</t>
+          <t>L450: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3270,16 +3230,12 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 1â€¢The balance of a line we sold at $12</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L513: symbol-only separator/garbage line :: 6.25</t>
+          <t>L451: symbol-only separator/garbage line :: 9.20</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3305,16 +3261,12 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: double/multiple hyphen | suspicious token(s): 50c (letter/digit mix) :: 1â€˜a yard reduced for this sale to 50c a --</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L521: symbol-only separator/garbage line :: 6.55</t>
+          <t>L452: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3340,16 +3292,12 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): 59c (letter/digit mix) :: â€¢ colors, at 59c each. â€¢</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L523: symbol-only separator/garbage line :: 8.15</t>
+          <t>L453: symbol-only separator/garbage line :: 10.30</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3375,16 +3323,12 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 75c (letter/digit mix) :: â€¢ Ladiesâ€™ Umbrellas at 75c each. *</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L529: symbol-only separator/garbage line :: 11.00</t>
+          <t>L454: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3410,16 +3354,12 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ $1.50 each. â€¢</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L533: isolated marker/symbol line :: D</t>
+          <t>L464: isolated marker/symbol line :: D.</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3445,16 +3385,12 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1200: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 5c (letter/digit mix) :: â€¢ Ladiesâ€™ Vests at 5c each Â°</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L582: isolated marker/symbol line :: E.</t>
+          <t>L484: symbol-only separator/garbage line :: 8.45</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3480,16 +3416,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1203: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: %each.â€¢</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L600: isolated marker/symbol line :: A.</t>
+          <t>L485: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3515,16 +3447,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ All kinds of Silk Lace Mitts, inâ€¢</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L607: isolated marker/symbol line :: D</t>
+          <t>L486: symbol-only separator/garbage line :: 9.65</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3550,16 +3478,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: : â€¢ black, cream and fawn, at cost. 1:</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L630: isolated marker/symbol line :: F</t>
+          <t>L487: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3585,16 +3509,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1207: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: %The balance of new Lace Curtainsâ€¢</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L683: isolated marker/symbol line :: D</t>
+          <t>L489: isolated marker/symbol line :: R.</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3620,16 +3540,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ at cost.</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L726: isolated marker/symbol line :: 7</t>
+          <t>L501: symbol-only separator/garbage line :: 2.50</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3655,16 +3571,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: = â€¢</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L786: isolated marker/symbol line :: R</t>
+          <t>L502: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3690,16 +3602,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1305: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tonic and blood purifier like Hoodâ€™s Sar-</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L837: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L503: symbol-only separator/garbage line :: 3.55</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3725,16 +3633,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1335: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to taste : stir till it boilsâ€”it should not</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L841: isolated marker/symbol line :: 4</t>
+          <t>L504: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3760,16 +3664,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1359: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Trebleâ€™s, corner King and James streets.</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L945: isolated marker/symbol line :: *</t>
+          <t>L511: isolated marker/symbol line :: 455</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3795,14 +3695,14 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Lew isâ€™ Cottee Tavern, King St. Station.</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>L512: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O67" s="1" t="inlineStr"/>
       <c r="P67" s="1" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr"/>
@@ -3826,14 +3726,14 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1428: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DO, Toronto, On*. Write for in " Set Sold iâ€”</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>L513: symbol-only separator/garbage line :: 6.25</t>
+        </is>
+      </c>
       <c r="O68" s="1" t="inlineStr"/>
       <c r="P68" s="1" t="inlineStr"/>
       <c r="Q68" s="1" t="inlineStr"/>
@@ -3846,6 +3746,626 @@
       <c r="X68" s="1" t="inlineStr"/>
       <c r="Y68" s="1" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr"/>
+      <c r="B69" s="1" t="inlineStr"/>
+      <c r="C69" s="1" t="inlineStr"/>
+      <c r="D69" s="1" t="inlineStr"/>
+      <c r="E69" s="1" t="inlineStr"/>
+      <c r="F69" s="1" t="inlineStr"/>
+      <c r="G69" s="1" t="inlineStr"/>
+      <c r="H69" s="1" t="inlineStr"/>
+      <c r="I69" s="1" t="inlineStr"/>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
+      <c r="L69" s="1" t="inlineStr"/>
+      <c r="M69" s="1" t="inlineStr"/>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>L514: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O69" s="1" t="inlineStr"/>
+      <c r="P69" s="1" t="inlineStr"/>
+      <c r="Q69" s="1" t="inlineStr"/>
+      <c r="R69" s="1" t="inlineStr"/>
+      <c r="S69" s="1" t="inlineStr"/>
+      <c r="T69" s="1" t="inlineStr"/>
+      <c r="U69" s="1" t="inlineStr"/>
+      <c r="V69" s="1" t="inlineStr"/>
+      <c r="W69" s="1" t="inlineStr"/>
+      <c r="X69" s="1" t="inlineStr"/>
+      <c r="Y69" s="1" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr"/>
+      <c r="B70" s="1" t="inlineStr"/>
+      <c r="C70" s="1" t="inlineStr"/>
+      <c r="D70" s="1" t="inlineStr"/>
+      <c r="E70" s="1" t="inlineStr"/>
+      <c r="F70" s="1" t="inlineStr"/>
+      <c r="G70" s="1" t="inlineStr"/>
+      <c r="H70" s="1" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr"/>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
+      <c r="L70" s="1" t="inlineStr"/>
+      <c r="M70" s="1" t="inlineStr"/>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>L521: symbol-only separator/garbage line :: 6.55</t>
+        </is>
+      </c>
+      <c r="O70" s="1" t="inlineStr"/>
+      <c r="P70" s="1" t="inlineStr"/>
+      <c r="Q70" s="1" t="inlineStr"/>
+      <c r="R70" s="1" t="inlineStr"/>
+      <c r="S70" s="1" t="inlineStr"/>
+      <c r="T70" s="1" t="inlineStr"/>
+      <c r="U70" s="1" t="inlineStr"/>
+      <c r="V70" s="1" t="inlineStr"/>
+      <c r="W70" s="1" t="inlineStr"/>
+      <c r="X70" s="1" t="inlineStr"/>
+      <c r="Y70" s="1" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr"/>
+      <c r="B71" s="1" t="inlineStr"/>
+      <c r="C71" s="1" t="inlineStr"/>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr"/>
+      <c r="F71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr"/>
+      <c r="H71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr"/>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
+      <c r="L71" s="1" t="inlineStr"/>
+      <c r="M71" s="1" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>L522: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O71" s="1" t="inlineStr"/>
+      <c r="P71" s="1" t="inlineStr"/>
+      <c r="Q71" s="1" t="inlineStr"/>
+      <c r="R71" s="1" t="inlineStr"/>
+      <c r="S71" s="1" t="inlineStr"/>
+      <c r="T71" s="1" t="inlineStr"/>
+      <c r="U71" s="1" t="inlineStr"/>
+      <c r="V71" s="1" t="inlineStr"/>
+      <c r="W71" s="1" t="inlineStr"/>
+      <c r="X71" s="1" t="inlineStr"/>
+      <c r="Y71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr"/>
+      <c r="B72" s="1" t="inlineStr"/>
+      <c r="C72" s="1" t="inlineStr"/>
+      <c r="D72" s="1" t="inlineStr"/>
+      <c r="E72" s="1" t="inlineStr"/>
+      <c r="F72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr"/>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
+      <c r="L72" s="1" t="inlineStr"/>
+      <c r="M72" s="1" t="inlineStr"/>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>L523: symbol-only separator/garbage line :: 8.15</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="inlineStr"/>
+      <c r="P72" s="1" t="inlineStr"/>
+      <c r="Q72" s="1" t="inlineStr"/>
+      <c r="R72" s="1" t="inlineStr"/>
+      <c r="S72" s="1" t="inlineStr"/>
+      <c r="T72" s="1" t="inlineStr"/>
+      <c r="U72" s="1" t="inlineStr"/>
+      <c r="V72" s="1" t="inlineStr"/>
+      <c r="W72" s="1" t="inlineStr"/>
+      <c r="X72" s="1" t="inlineStr"/>
+      <c r="Y72" s="1" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr"/>
+      <c r="B73" s="1" t="inlineStr"/>
+      <c r="C73" s="1" t="inlineStr"/>
+      <c r="D73" s="1" t="inlineStr"/>
+      <c r="E73" s="1" t="inlineStr"/>
+      <c r="F73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr"/>
+      <c r="H73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr"/>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
+      <c r="L73" s="1" t="inlineStr"/>
+      <c r="M73" s="1" t="inlineStr"/>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>L524: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="inlineStr"/>
+      <c r="P73" s="1" t="inlineStr"/>
+      <c r="Q73" s="1" t="inlineStr"/>
+      <c r="R73" s="1" t="inlineStr"/>
+      <c r="S73" s="1" t="inlineStr"/>
+      <c r="T73" s="1" t="inlineStr"/>
+      <c r="U73" s="1" t="inlineStr"/>
+      <c r="V73" s="1" t="inlineStr"/>
+      <c r="W73" s="1" t="inlineStr"/>
+      <c r="X73" s="1" t="inlineStr"/>
+      <c r="Y73" s="1" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr"/>
+      <c r="B74" s="1" t="inlineStr"/>
+      <c r="C74" s="1" t="inlineStr"/>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr"/>
+      <c r="F74" s="1" t="inlineStr"/>
+      <c r="G74" s="1" t="inlineStr"/>
+      <c r="H74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr"/>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
+      <c r="L74" s="1" t="inlineStr"/>
+      <c r="M74" s="1" t="inlineStr"/>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t>L529: symbol-only separator/garbage line :: 11.00</t>
+        </is>
+      </c>
+      <c r="O74" s="1" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr"/>
+      <c r="Q74" s="1" t="inlineStr"/>
+      <c r="R74" s="1" t="inlineStr"/>
+      <c r="S74" s="1" t="inlineStr"/>
+      <c r="T74" s="1" t="inlineStr"/>
+      <c r="U74" s="1" t="inlineStr"/>
+      <c r="V74" s="1" t="inlineStr"/>
+      <c r="W74" s="1" t="inlineStr"/>
+      <c r="X74" s="1" t="inlineStr"/>
+      <c r="Y74" s="1" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr"/>
+      <c r="B75" s="1" t="inlineStr"/>
+      <c r="C75" s="1" t="inlineStr"/>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr"/>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr"/>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
+      <c r="L75" s="1" t="inlineStr"/>
+      <c r="M75" s="1" t="inlineStr"/>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t>L530: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O75" s="1" t="inlineStr"/>
+      <c r="P75" s="1" t="inlineStr"/>
+      <c r="Q75" s="1" t="inlineStr"/>
+      <c r="R75" s="1" t="inlineStr"/>
+      <c r="S75" s="1" t="inlineStr"/>
+      <c r="T75" s="1" t="inlineStr"/>
+      <c r="U75" s="1" t="inlineStr"/>
+      <c r="V75" s="1" t="inlineStr"/>
+      <c r="W75" s="1" t="inlineStr"/>
+      <c r="X75" s="1" t="inlineStr"/>
+      <c r="Y75" s="1" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr"/>
+      <c r="B76" s="1" t="inlineStr"/>
+      <c r="C76" s="1" t="inlineStr"/>
+      <c r="D76" s="1" t="inlineStr"/>
+      <c r="E76" s="1" t="inlineStr"/>
+      <c r="F76" s="1" t="inlineStr"/>
+      <c r="G76" s="1" t="inlineStr"/>
+      <c r="H76" s="1" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr"/>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
+      <c r="L76" s="1" t="inlineStr"/>
+      <c r="M76" s="1" t="inlineStr"/>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>L533: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O76" s="1" t="inlineStr"/>
+      <c r="P76" s="1" t="inlineStr"/>
+      <c r="Q76" s="1" t="inlineStr"/>
+      <c r="R76" s="1" t="inlineStr"/>
+      <c r="S76" s="1" t="inlineStr"/>
+      <c r="T76" s="1" t="inlineStr"/>
+      <c r="U76" s="1" t="inlineStr"/>
+      <c r="V76" s="1" t="inlineStr"/>
+      <c r="W76" s="1" t="inlineStr"/>
+      <c r="X76" s="1" t="inlineStr"/>
+      <c r="Y76" s="1" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr"/>
+      <c r="B77" s="1" t="inlineStr"/>
+      <c r="C77" s="1" t="inlineStr"/>
+      <c r="D77" s="1" t="inlineStr"/>
+      <c r="E77" s="1" t="inlineStr"/>
+      <c r="F77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr"/>
+      <c r="H77" s="1" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr"/>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
+      <c r="L77" s="1" t="inlineStr"/>
+      <c r="M77" s="1" t="inlineStr"/>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>L582: isolated marker/symbol line :: E.</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="inlineStr"/>
+      <c r="P77" s="1" t="inlineStr"/>
+      <c r="Q77" s="1" t="inlineStr"/>
+      <c r="R77" s="1" t="inlineStr"/>
+      <c r="S77" s="1" t="inlineStr"/>
+      <c r="T77" s="1" t="inlineStr"/>
+      <c r="U77" s="1" t="inlineStr"/>
+      <c r="V77" s="1" t="inlineStr"/>
+      <c r="W77" s="1" t="inlineStr"/>
+      <c r="X77" s="1" t="inlineStr"/>
+      <c r="Y77" s="1" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr"/>
+      <c r="B78" s="1" t="inlineStr"/>
+      <c r="C78" s="1" t="inlineStr"/>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr"/>
+      <c r="F78" s="1" t="inlineStr"/>
+      <c r="G78" s="1" t="inlineStr"/>
+      <c r="H78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr"/>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
+      <c r="L78" s="1" t="inlineStr"/>
+      <c r="M78" s="1" t="inlineStr"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>L600: isolated marker/symbol line :: A.</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="inlineStr"/>
+      <c r="P78" s="1" t="inlineStr"/>
+      <c r="Q78" s="1" t="inlineStr"/>
+      <c r="R78" s="1" t="inlineStr"/>
+      <c r="S78" s="1" t="inlineStr"/>
+      <c r="T78" s="1" t="inlineStr"/>
+      <c r="U78" s="1" t="inlineStr"/>
+      <c r="V78" s="1" t="inlineStr"/>
+      <c r="W78" s="1" t="inlineStr"/>
+      <c r="X78" s="1" t="inlineStr"/>
+      <c r="Y78" s="1" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr"/>
+      <c r="B79" s="1" t="inlineStr"/>
+      <c r="C79" s="1" t="inlineStr"/>
+      <c r="D79" s="1" t="inlineStr"/>
+      <c r="E79" s="1" t="inlineStr"/>
+      <c r="F79" s="1" t="inlineStr"/>
+      <c r="G79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr"/>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
+      <c r="L79" s="1" t="inlineStr"/>
+      <c r="M79" s="1" t="inlineStr"/>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>L607: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr"/>
+      <c r="R79" s="1" t="inlineStr"/>
+      <c r="S79" s="1" t="inlineStr"/>
+      <c r="T79" s="1" t="inlineStr"/>
+      <c r="U79" s="1" t="inlineStr"/>
+      <c r="V79" s="1" t="inlineStr"/>
+      <c r="W79" s="1" t="inlineStr"/>
+      <c r="X79" s="1" t="inlineStr"/>
+      <c r="Y79" s="1" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr"/>
+      <c r="B80" s="1" t="inlineStr"/>
+      <c r="C80" s="1" t="inlineStr"/>
+      <c r="D80" s="1" t="inlineStr"/>
+      <c r="E80" s="1" t="inlineStr"/>
+      <c r="F80" s="1" t="inlineStr"/>
+      <c r="G80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr"/>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
+      <c r="L80" s="1" t="inlineStr"/>
+      <c r="M80" s="1" t="inlineStr"/>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>L630: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr"/>
+      <c r="P80" s="1" t="inlineStr"/>
+      <c r="Q80" s="1" t="inlineStr"/>
+      <c r="R80" s="1" t="inlineStr"/>
+      <c r="S80" s="1" t="inlineStr"/>
+      <c r="T80" s="1" t="inlineStr"/>
+      <c r="U80" s="1" t="inlineStr"/>
+      <c r="V80" s="1" t="inlineStr"/>
+      <c r="W80" s="1" t="inlineStr"/>
+      <c r="X80" s="1" t="inlineStr"/>
+      <c r="Y80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr"/>
+      <c r="B81" s="1" t="inlineStr"/>
+      <c r="C81" s="1" t="inlineStr"/>
+      <c r="D81" s="1" t="inlineStr"/>
+      <c r="E81" s="1" t="inlineStr"/>
+      <c r="F81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr"/>
+      <c r="H81" s="1" t="inlineStr"/>
+      <c r="I81" s="1" t="inlineStr"/>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
+      <c r="L81" s="1" t="inlineStr"/>
+      <c r="M81" s="1" t="inlineStr"/>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>L683: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O81" s="1" t="inlineStr"/>
+      <c r="P81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="inlineStr"/>
+      <c r="R81" s="1" t="inlineStr"/>
+      <c r="S81" s="1" t="inlineStr"/>
+      <c r="T81" s="1" t="inlineStr"/>
+      <c r="U81" s="1" t="inlineStr"/>
+      <c r="V81" s="1" t="inlineStr"/>
+      <c r="W81" s="1" t="inlineStr"/>
+      <c r="X81" s="1" t="inlineStr"/>
+      <c r="Y81" s="1" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr"/>
+      <c r="B82" s="1" t="inlineStr"/>
+      <c r="C82" s="1" t="inlineStr"/>
+      <c r="D82" s="1" t="inlineStr"/>
+      <c r="E82" s="1" t="inlineStr"/>
+      <c r="F82" s="1" t="inlineStr"/>
+      <c r="G82" s="1" t="inlineStr"/>
+      <c r="H82" s="1" t="inlineStr"/>
+      <c r="I82" s="1" t="inlineStr"/>
+      <c r="J82" s="1" t="inlineStr"/>
+      <c r="K82" s="1" t="inlineStr"/>
+      <c r="L82" s="1" t="inlineStr"/>
+      <c r="M82" s="1" t="inlineStr"/>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>L726: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr"/>
+      <c r="P82" s="1" t="inlineStr"/>
+      <c r="Q82" s="1" t="inlineStr"/>
+      <c r="R82" s="1" t="inlineStr"/>
+      <c r="S82" s="1" t="inlineStr"/>
+      <c r="T82" s="1" t="inlineStr"/>
+      <c r="U82" s="1" t="inlineStr"/>
+      <c r="V82" s="1" t="inlineStr"/>
+      <c r="W82" s="1" t="inlineStr"/>
+      <c r="X82" s="1" t="inlineStr"/>
+      <c r="Y82" s="1" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr"/>
+      <c r="B83" s="1" t="inlineStr"/>
+      <c r="C83" s="1" t="inlineStr"/>
+      <c r="D83" s="1" t="inlineStr"/>
+      <c r="E83" s="1" t="inlineStr"/>
+      <c r="F83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr"/>
+      <c r="H83" s="1" t="inlineStr"/>
+      <c r="I83" s="1" t="inlineStr"/>
+      <c r="J83" s="1" t="inlineStr"/>
+      <c r="K83" s="1" t="inlineStr"/>
+      <c r="L83" s="1" t="inlineStr"/>
+      <c r="M83" s="1" t="inlineStr"/>
+      <c r="N83" s="1" t="inlineStr">
+        <is>
+          <t>L786: isolated marker/symbol line :: R</t>
+        </is>
+      </c>
+      <c r="O83" s="1" t="inlineStr"/>
+      <c r="P83" s="1" t="inlineStr"/>
+      <c r="Q83" s="1" t="inlineStr"/>
+      <c r="R83" s="1" t="inlineStr"/>
+      <c r="S83" s="1" t="inlineStr"/>
+      <c r="T83" s="1" t="inlineStr"/>
+      <c r="U83" s="1" t="inlineStr"/>
+      <c r="V83" s="1" t="inlineStr"/>
+      <c r="W83" s="1" t="inlineStr"/>
+      <c r="X83" s="1" t="inlineStr"/>
+      <c r="Y83" s="1" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr"/>
+      <c r="B84" s="1" t="inlineStr"/>
+      <c r="C84" s="1" t="inlineStr"/>
+      <c r="D84" s="1" t="inlineStr"/>
+      <c r="E84" s="1" t="inlineStr"/>
+      <c r="F84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr"/>
+      <c r="H84" s="1" t="inlineStr"/>
+      <c r="I84" s="1" t="inlineStr"/>
+      <c r="J84" s="1" t="inlineStr"/>
+      <c r="K84" s="1" t="inlineStr"/>
+      <c r="L84" s="1" t="inlineStr"/>
+      <c r="M84" s="1" t="inlineStr"/>
+      <c r="N84" s="1" t="inlineStr">
+        <is>
+          <t>L837: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O84" s="1" t="inlineStr"/>
+      <c r="P84" s="1" t="inlineStr"/>
+      <c r="Q84" s="1" t="inlineStr"/>
+      <c r="R84" s="1" t="inlineStr"/>
+      <c r="S84" s="1" t="inlineStr"/>
+      <c r="T84" s="1" t="inlineStr"/>
+      <c r="U84" s="1" t="inlineStr"/>
+      <c r="V84" s="1" t="inlineStr"/>
+      <c r="W84" s="1" t="inlineStr"/>
+      <c r="X84" s="1" t="inlineStr"/>
+      <c r="Y84" s="1" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr"/>
+      <c r="B85" s="1" t="inlineStr"/>
+      <c r="C85" s="1" t="inlineStr"/>
+      <c r="D85" s="1" t="inlineStr"/>
+      <c r="E85" s="1" t="inlineStr"/>
+      <c r="F85" s="1" t="inlineStr"/>
+      <c r="G85" s="1" t="inlineStr"/>
+      <c r="H85" s="1" t="inlineStr"/>
+      <c r="I85" s="1" t="inlineStr"/>
+      <c r="J85" s="1" t="inlineStr"/>
+      <c r="K85" s="1" t="inlineStr"/>
+      <c r="L85" s="1" t="inlineStr"/>
+      <c r="M85" s="1" t="inlineStr"/>
+      <c r="N85" s="1" t="inlineStr">
+        <is>
+          <t>L841: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O85" s="1" t="inlineStr"/>
+      <c r="P85" s="1" t="inlineStr"/>
+      <c r="Q85" s="1" t="inlineStr"/>
+      <c r="R85" s="1" t="inlineStr"/>
+      <c r="S85" s="1" t="inlineStr"/>
+      <c r="T85" s="1" t="inlineStr"/>
+      <c r="U85" s="1" t="inlineStr"/>
+      <c r="V85" s="1" t="inlineStr"/>
+      <c r="W85" s="1" t="inlineStr"/>
+      <c r="X85" s="1" t="inlineStr"/>
+      <c r="Y85" s="1" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr"/>
+      <c r="B86" s="1" t="inlineStr"/>
+      <c r="C86" s="1" t="inlineStr"/>
+      <c r="D86" s="1" t="inlineStr"/>
+      <c r="E86" s="1" t="inlineStr"/>
+      <c r="F86" s="1" t="inlineStr"/>
+      <c r="G86" s="1" t="inlineStr"/>
+      <c r="H86" s="1" t="inlineStr"/>
+      <c r="I86" s="1" t="inlineStr"/>
+      <c r="J86" s="1" t="inlineStr"/>
+      <c r="K86" s="1" t="inlineStr"/>
+      <c r="L86" s="1" t="inlineStr"/>
+      <c r="M86" s="1" t="inlineStr"/>
+      <c r="N86" s="1" t="inlineStr">
+        <is>
+          <t>L844: stray/suspicious non-ASCII glyph(s): U+96EA CJK UNIFIED IDEOGRAPH-96EA | isolated marker/symbol line :: 雪</t>
+        </is>
+      </c>
+      <c r="O86" s="1" t="inlineStr"/>
+      <c r="P86" s="1" t="inlineStr"/>
+      <c r="Q86" s="1" t="inlineStr"/>
+      <c r="R86" s="1" t="inlineStr"/>
+      <c r="S86" s="1" t="inlineStr"/>
+      <c r="T86" s="1" t="inlineStr"/>
+      <c r="U86" s="1" t="inlineStr"/>
+      <c r="V86" s="1" t="inlineStr"/>
+      <c r="W86" s="1" t="inlineStr"/>
+      <c r="X86" s="1" t="inlineStr"/>
+      <c r="Y86" s="1" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr"/>
+      <c r="B87" s="1" t="inlineStr"/>
+      <c r="C87" s="1" t="inlineStr"/>
+      <c r="D87" s="1" t="inlineStr"/>
+      <c r="E87" s="1" t="inlineStr"/>
+      <c r="F87" s="1" t="inlineStr"/>
+      <c r="G87" s="1" t="inlineStr"/>
+      <c r="H87" s="1" t="inlineStr"/>
+      <c r="I87" s="1" t="inlineStr"/>
+      <c r="J87" s="1" t="inlineStr"/>
+      <c r="K87" s="1" t="inlineStr"/>
+      <c r="L87" s="1" t="inlineStr"/>
+      <c r="M87" s="1" t="inlineStr"/>
+      <c r="N87" s="1" t="inlineStr">
+        <is>
+          <t>L908: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
+        </is>
+      </c>
+      <c r="O87" s="1" t="inlineStr"/>
+      <c r="P87" s="1" t="inlineStr"/>
+      <c r="Q87" s="1" t="inlineStr"/>
+      <c r="R87" s="1" t="inlineStr"/>
+      <c r="S87" s="1" t="inlineStr"/>
+      <c r="T87" s="1" t="inlineStr"/>
+      <c r="U87" s="1" t="inlineStr"/>
+      <c r="V87" s="1" t="inlineStr"/>
+      <c r="W87" s="1" t="inlineStr"/>
+      <c r="X87" s="1" t="inlineStr"/>
+      <c r="Y87" s="1" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr"/>
+      <c r="B88" s="1" t="inlineStr"/>
+      <c r="C88" s="1" t="inlineStr"/>
+      <c r="D88" s="1" t="inlineStr"/>
+      <c r="E88" s="1" t="inlineStr"/>
+      <c r="F88" s="1" t="inlineStr"/>
+      <c r="G88" s="1" t="inlineStr"/>
+      <c r="H88" s="1" t="inlineStr"/>
+      <c r="I88" s="1" t="inlineStr"/>
+      <c r="J88" s="1" t="inlineStr"/>
+      <c r="K88" s="1" t="inlineStr"/>
+      <c r="L88" s="1" t="inlineStr"/>
+      <c r="M88" s="1" t="inlineStr"/>
+      <c r="N88" s="1" t="inlineStr">
+        <is>
+          <t>L945: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
+      <c r="O88" s="1" t="inlineStr"/>
+      <c r="P88" s="1" t="inlineStr"/>
+      <c r="Q88" s="1" t="inlineStr"/>
+      <c r="R88" s="1" t="inlineStr"/>
+      <c r="S88" s="1" t="inlineStr"/>
+      <c r="T88" s="1" t="inlineStr"/>
+      <c r="U88" s="1" t="inlineStr"/>
+      <c r="V88" s="1" t="inlineStr"/>
+      <c r="W88" s="1" t="inlineStr"/>
+      <c r="X88" s="1" t="inlineStr"/>
+      <c r="Y88" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
